--- a/astro-site/public/dl/plan-chef-privado-showcooking-eventos/plan-financiero-chef-privado-showcooking.xlsx
+++ b/astro-site/public/dl/plan-chef-privado-showcooking-eventos/plan-financiero-chef-privado-showcooking.xlsx
@@ -14,7 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mix B2C-B2B" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Resumen'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'P&amp;L Año 1'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Proyección 3 años'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Mix B2C-B2B'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'KPIs'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -535,7 +541,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -562,6 +568,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -618,7 +625,7 @@
       </c>
       <c r="E6" s="7">
         <f>D6/$D$17</f>
-        <v/>
+        <v>0.028638814016172506</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -643,7 +650,7 @@
       </c>
       <c r="E7" s="7">
         <f>D7/$D$17</f>
-        <v/>
+        <v>0.07412398921832884</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -668,7 +675,7 @@
       </c>
       <c r="E8" s="7">
         <f>D8/$D$17</f>
-        <v/>
+        <v>0.038746630727762806</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -693,7 +700,7 @@
       </c>
       <c r="E9" s="7">
         <f>D9/$D$17</f>
-        <v/>
+        <v>0.045485175202156336</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -718,7 +725,7 @@
       </c>
       <c r="E10" s="7">
         <f>D10/$D$17</f>
-        <v/>
+        <v>0.08086253369272237</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -743,7 +750,7 @@
       </c>
       <c r="E11" s="7">
         <f>D11/$D$17</f>
-        <v/>
+        <v>0.03706199460916442</v>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
@@ -768,7 +775,7 @@
       </c>
       <c r="E12" s="7">
         <f>D12/$D$17</f>
-        <v/>
+        <v>0.03975741239892183</v>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
@@ -793,7 +800,7 @@
       </c>
       <c r="E13" s="7">
         <f>D13/$D$17</f>
-        <v/>
+        <v>0.028638814016172506</v>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
@@ -818,7 +825,7 @@
       </c>
       <c r="E14" s="7">
         <f>D14/$D$17</f>
-        <v/>
+        <v>0.14150943396226415</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -843,7 +850,7 @@
       </c>
       <c r="E15" s="7">
         <f>D15/$D$17</f>
-        <v/>
+        <v>0.08086253369272237</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -868,7 +875,7 @@
       </c>
       <c r="E16" s="7">
         <f>D16/$D$17</f>
-        <v/>
+        <v>0.40431266846361186</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -884,15 +891,15 @@
       </c>
       <c r="B17" s="9">
         <f>SUM(B6:B16)</f>
-        <v/>
+        <v>4690.0</v>
       </c>
       <c r="C17" s="9">
         <f>SUM(C6:C16)</f>
-        <v/>
+        <v>11580.0</v>
       </c>
       <c r="D17" s="9">
         <f>SUM(D6:D16)</f>
-        <v/>
+        <v>29680.0</v>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
@@ -903,11 +910,20 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -915,7 +931,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -950,6 +966,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1066,7 +1083,7 @@
       </c>
       <c r="N5" s="12">
         <f>SUM(B5:M5)</f>
-        <v/>
+        <v>42920.0</v>
       </c>
     </row>
     <row r="6">
@@ -1113,7 +1130,7 @@
       </c>
       <c r="N6" s="12">
         <f>SUM(B6:M6)</f>
-        <v/>
+        <v>114550.0</v>
       </c>
     </row>
     <row r="7">
@@ -1124,57 +1141,58 @@
       </c>
       <c r="B7" s="14">
         <f>SUM(B5:B6)</f>
-        <v/>
+        <v>6670.0</v>
       </c>
       <c r="C7" s="14">
         <f>SUM(C5:C6)</f>
-        <v/>
+        <v>8120.0</v>
       </c>
       <c r="D7" s="14">
         <f>SUM(D5:D6)</f>
-        <v/>
+        <v>10150.0</v>
       </c>
       <c r="E7" s="14">
         <f>SUM(E5:E6)</f>
-        <v/>
+        <v>11600.0</v>
       </c>
       <c r="F7" s="14">
         <f>SUM(F5:F6)</f>
-        <v/>
+        <v>13630.0</v>
       </c>
       <c r="G7" s="14">
         <f>SUM(G5:G6)</f>
-        <v/>
+        <v>17690.0</v>
       </c>
       <c r="H7" s="14">
         <f>SUM(H5:H6)</f>
-        <v/>
+        <v>12760.0</v>
       </c>
       <c r="I7" s="14">
         <f>SUM(I5:I6)</f>
-        <v/>
+        <v>8700.0</v>
       </c>
       <c r="J7" s="14">
         <f>SUM(J5:J6)</f>
-        <v/>
+        <v>13630.0</v>
       </c>
       <c r="K7" s="14">
         <f>SUM(K5:K6)</f>
-        <v/>
+        <v>15080.0</v>
       </c>
       <c r="L7" s="14">
         <f>SUM(L5:L6)</f>
-        <v/>
+        <v>15660.0</v>
       </c>
       <c r="M7" s="14">
         <f>SUM(M5:M6)</f>
-        <v/>
+        <v>23780.0</v>
       </c>
       <c r="N7" s="14">
         <f>SUM(N5:N6)</f>
-        <v/>
-      </c>
-    </row>
+        <v>157470.0</v>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
@@ -1183,55 +1201,55 @@
       </c>
       <c r="B9" s="12">
         <f>B7*0.26</f>
-        <v/>
+        <v>1734.2</v>
       </c>
       <c r="C9" s="12">
         <f>C7*0.26</f>
-        <v/>
+        <v>2111.2000000000003</v>
       </c>
       <c r="D9" s="12">
         <f>D7*0.26</f>
-        <v/>
+        <v>2639.0</v>
       </c>
       <c r="E9" s="12">
         <f>E7*0.26</f>
-        <v/>
+        <v>3016.0</v>
       </c>
       <c r="F9" s="12">
         <f>F7*0.26</f>
-        <v/>
+        <v>3543.8</v>
       </c>
       <c r="G9" s="12">
         <f>G7*0.26</f>
-        <v/>
+        <v>4599.400000000001</v>
       </c>
       <c r="H9" s="12">
         <f>H7*0.26</f>
-        <v/>
+        <v>3317.6</v>
       </c>
       <c r="I9" s="12">
         <f>I7*0.26</f>
-        <v/>
+        <v>2262.0</v>
       </c>
       <c r="J9" s="12">
         <f>J7*0.26</f>
-        <v/>
+        <v>3543.8</v>
       </c>
       <c r="K9" s="12">
         <f>K7*0.26</f>
-        <v/>
+        <v>3920.8</v>
       </c>
       <c r="L9" s="12">
         <f>L7*0.26</f>
-        <v/>
+        <v>4071.6000000000004</v>
       </c>
       <c r="M9" s="12">
         <f>M7*0.26</f>
-        <v/>
+        <v>6182.8</v>
       </c>
       <c r="N9" s="12">
         <f>N7*0.26</f>
-        <v/>
+        <v>40942.200000000004</v>
       </c>
     </row>
     <row r="10">
@@ -1242,55 +1260,55 @@
       </c>
       <c r="B10" s="12">
         <f>B7*0.04</f>
-        <v/>
+        <v>266.8</v>
       </c>
       <c r="C10" s="12">
         <f>C7*0.04</f>
-        <v/>
+        <v>324.8</v>
       </c>
       <c r="D10" s="12">
         <f>D7*0.04</f>
-        <v/>
+        <v>406.0</v>
       </c>
       <c r="E10" s="12">
         <f>E7*0.04</f>
-        <v/>
+        <v>464.0</v>
       </c>
       <c r="F10" s="12">
         <f>F7*0.04</f>
-        <v/>
+        <v>545.2</v>
       </c>
       <c r="G10" s="12">
         <f>G7*0.04</f>
-        <v/>
+        <v>707.6</v>
       </c>
       <c r="H10" s="12">
         <f>H7*0.04</f>
-        <v/>
+        <v>510.40000000000003</v>
       </c>
       <c r="I10" s="12">
         <f>I7*0.04</f>
-        <v/>
+        <v>348.0</v>
       </c>
       <c r="J10" s="12">
         <f>J7*0.04</f>
-        <v/>
+        <v>545.2</v>
       </c>
       <c r="K10" s="12">
         <f>K7*0.04</f>
-        <v/>
+        <v>603.2</v>
       </c>
       <c r="L10" s="12">
         <f>L7*0.04</f>
-        <v/>
+        <v>626.4</v>
       </c>
       <c r="M10" s="12">
         <f>M7*0.04</f>
-        <v/>
+        <v>951.2</v>
       </c>
       <c r="N10" s="12">
         <f>N7*0.04</f>
-        <v/>
+        <v>6298.8</v>
       </c>
     </row>
     <row r="11">
@@ -1301,57 +1319,58 @@
       </c>
       <c r="B11" s="12">
         <f>B7*0.08</f>
-        <v/>
+        <v>533.6</v>
       </c>
       <c r="C11" s="12">
         <f>C7*0.08</f>
-        <v/>
+        <v>649.6</v>
       </c>
       <c r="D11" s="12">
         <f>D7*0.08</f>
-        <v/>
+        <v>812.0</v>
       </c>
       <c r="E11" s="12">
         <f>E7*0.08</f>
-        <v/>
+        <v>928.0</v>
       </c>
       <c r="F11" s="12">
         <f>F7*0.08</f>
-        <v/>
+        <v>1090.4</v>
       </c>
       <c r="G11" s="12">
         <f>G7*0.08</f>
-        <v/>
+        <v>1415.2</v>
       </c>
       <c r="H11" s="12">
         <f>H7*0.08</f>
-        <v/>
+        <v>1020.8000000000001</v>
       </c>
       <c r="I11" s="12">
         <f>I7*0.08</f>
-        <v/>
+        <v>696.0</v>
       </c>
       <c r="J11" s="12">
         <f>J7*0.08</f>
-        <v/>
+        <v>1090.4</v>
       </c>
       <c r="K11" s="12">
         <f>K7*0.08</f>
-        <v/>
+        <v>1206.4</v>
       </c>
       <c r="L11" s="12">
         <f>L7*0.08</f>
-        <v/>
+        <v>1252.8</v>
       </c>
       <c r="M11" s="12">
         <f>M7*0.08</f>
-        <v/>
+        <v>1902.4</v>
       </c>
       <c r="N11" s="12">
         <f>N7*0.08</f>
-        <v/>
-      </c>
-    </row>
+        <v>12597.6</v>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -1396,7 +1415,7 @@
       </c>
       <c r="N13" s="12">
         <f>SUM(B13:M13)</f>
-        <v/>
+        <v>960.0</v>
       </c>
     </row>
     <row r="14">
@@ -1443,7 +1462,7 @@
       </c>
       <c r="N14" s="12">
         <f>SUM(B14:M14)</f>
-        <v/>
+        <v>1320.0</v>
       </c>
     </row>
     <row r="15">
@@ -1490,7 +1509,7 @@
       </c>
       <c r="N15" s="12">
         <f>SUM(B15:M15)</f>
-        <v/>
+        <v>2160.0</v>
       </c>
     </row>
     <row r="16">
@@ -1537,9 +1556,10 @@
       </c>
       <c r="N16" s="12">
         <f>SUM(B16:M16)</f>
-        <v/>
-      </c>
-    </row>
+        <v>3360.0</v>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -1548,55 +1568,55 @@
       </c>
       <c r="B18" s="14">
         <f>SUM(B9:B11)+SUM(B13:B16)</f>
-        <v/>
+        <v>3184.6</v>
       </c>
       <c r="C18" s="14">
         <f>SUM(C9:C11)+SUM(C13:C16)</f>
-        <v/>
+        <v>3735.6000000000004</v>
       </c>
       <c r="D18" s="14">
         <f>SUM(D9:D11)+SUM(D13:D16)</f>
-        <v/>
+        <v>4507.0</v>
       </c>
       <c r="E18" s="14">
         <f>SUM(E9:E11)+SUM(E13:E16)</f>
-        <v/>
+        <v>5058.0</v>
       </c>
       <c r="F18" s="14">
         <f>SUM(F9:F11)+SUM(F13:F16)</f>
-        <v/>
+        <v>5829.4</v>
       </c>
       <c r="G18" s="14">
         <f>SUM(G9:G11)+SUM(G13:G16)</f>
-        <v/>
+        <v>7372.200000000001</v>
       </c>
       <c r="H18" s="14">
         <f>SUM(H9:H11)+SUM(H13:H16)</f>
-        <v/>
+        <v>5498.8</v>
       </c>
       <c r="I18" s="14">
         <f>SUM(I9:I11)+SUM(I13:I16)</f>
-        <v/>
+        <v>3956.0</v>
       </c>
       <c r="J18" s="14">
         <f>SUM(J9:J11)+SUM(J13:J16)</f>
-        <v/>
+        <v>5829.4</v>
       </c>
       <c r="K18" s="14">
         <f>SUM(K9:K11)+SUM(K13:K16)</f>
-        <v/>
+        <v>6380.4</v>
       </c>
       <c r="L18" s="14">
         <f>SUM(L9:L11)+SUM(L13:L16)</f>
-        <v/>
+        <v>6600.8</v>
       </c>
       <c r="M18" s="14">
         <f>SUM(M9:M11)+SUM(M13:M16)</f>
-        <v/>
+        <v>9686.4</v>
       </c>
       <c r="N18" s="14">
         <f>SUM(N9:N11)+SUM(N13:N16)</f>
-        <v/>
+        <v>67638.6</v>
       </c>
     </row>
     <row r="19">
@@ -1607,63 +1627,72 @@
       </c>
       <c r="B19" s="15">
         <f>B7-B18</f>
-        <v/>
+        <v>3485.4</v>
       </c>
       <c r="C19" s="15">
         <f>C7-C18</f>
-        <v/>
+        <v>4384.4</v>
       </c>
       <c r="D19" s="15">
         <f>D7-D18</f>
-        <v/>
+        <v>5643.0</v>
       </c>
       <c r="E19" s="15">
         <f>E7-E18</f>
-        <v/>
+        <v>6542.0</v>
       </c>
       <c r="F19" s="15">
         <f>F7-F18</f>
-        <v/>
+        <v>7800.6</v>
       </c>
       <c r="G19" s="15">
         <f>G7-G18</f>
-        <v/>
+        <v>10317.8</v>
       </c>
       <c r="H19" s="15">
         <f>H7-H18</f>
-        <v/>
+        <v>7261.2</v>
       </c>
       <c r="I19" s="15">
         <f>I7-I18</f>
-        <v/>
+        <v>4744.0</v>
       </c>
       <c r="J19" s="15">
         <f>J7-J18</f>
-        <v/>
+        <v>7800.6</v>
       </c>
       <c r="K19" s="15">
         <f>K7-K18</f>
-        <v/>
+        <v>8699.6</v>
       </c>
       <c r="L19" s="15">
         <f>L7-L18</f>
-        <v/>
+        <v>9059.2</v>
       </c>
       <c r="M19" s="15">
         <f>M7-M18</f>
-        <v/>
+        <v>14093.6</v>
       </c>
       <c r="N19" s="15">
         <f>N7-N18</f>
-        <v/>
+        <v>89831.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1671,7 +1700,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1696,6 +1725,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1790,15 +1820,15 @@
       </c>
       <c r="B9" s="6">
         <f>B5*B7</f>
-        <v/>
+        <v>42920.0</v>
       </c>
       <c r="C9" s="6">
         <f>C5*C7</f>
-        <v/>
+        <v>60800.0</v>
       </c>
       <c r="D9" s="6">
         <f>D5*D7</f>
-        <v/>
+        <v>80500.0</v>
       </c>
     </row>
     <row r="10">
@@ -1809,15 +1839,15 @@
       </c>
       <c r="B10" s="6">
         <f>B6*B8</f>
-        <v/>
+        <v>114550.0</v>
       </c>
       <c r="C10" s="6">
         <f>C6*C8</f>
-        <v/>
+        <v>158000.0</v>
       </c>
       <c r="D10" s="6">
         <f>D6*D8</f>
-        <v/>
+        <v>213500.0</v>
       </c>
     </row>
     <row r="11">
@@ -1828,15 +1858,15 @@
       </c>
       <c r="B11" s="9">
         <f>B9+B10</f>
-        <v/>
+        <v>157470.0</v>
       </c>
       <c r="C11" s="9">
         <f>C9+C10</f>
-        <v/>
+        <v>218800.0</v>
       </c>
       <c r="D11" s="9">
         <f>D9+D10</f>
-        <v/>
+        <v>294000.0</v>
       </c>
     </row>
     <row r="12">
@@ -1847,15 +1877,15 @@
       </c>
       <c r="B12" s="6">
         <f>B11*0.26</f>
-        <v/>
+        <v>40942.200000000004</v>
       </c>
       <c r="C12" s="6">
         <f>C11*0.25</f>
-        <v/>
+        <v>54700.0</v>
       </c>
       <c r="D12" s="6">
         <f>D11*0.24</f>
-        <v/>
+        <v>70560.0</v>
       </c>
     </row>
     <row r="13">
@@ -1866,15 +1896,15 @@
       </c>
       <c r="B13" s="6">
         <f>B11*0.04</f>
-        <v/>
+        <v>6298.8</v>
       </c>
       <c r="C13" s="6">
         <f>C11*0.04</f>
-        <v/>
+        <v>8752.0</v>
       </c>
       <c r="D13" s="6">
         <f>D11*0.04</f>
-        <v/>
+        <v>11760.0</v>
       </c>
     </row>
     <row r="14">
@@ -1885,15 +1915,15 @@
       </c>
       <c r="B14" s="6">
         <f>B11*0.08</f>
-        <v/>
+        <v>12597.6</v>
       </c>
       <c r="C14" s="6">
         <f>C11*0.09</f>
-        <v/>
+        <v>19692.0</v>
       </c>
       <c r="D14" s="6">
         <f>D11*0.10</f>
-        <v/>
+        <v>29400.0</v>
       </c>
     </row>
     <row r="15">
@@ -1920,15 +1950,15 @@
       </c>
       <c r="B16" s="9">
         <f>SUM(B12:B15)</f>
-        <v/>
+        <v>67638.6</v>
       </c>
       <c r="C16" s="9">
         <f>SUM(C12:C15)</f>
-        <v/>
+        <v>91944.0</v>
       </c>
       <c r="D16" s="9">
         <f>SUM(D12:D15)</f>
-        <v/>
+        <v>122220.0</v>
       </c>
     </row>
     <row r="17">
@@ -1939,15 +1969,15 @@
       </c>
       <c r="B17" s="17">
         <f>B11-B16</f>
-        <v/>
+        <v>89831.4</v>
       </c>
       <c r="C17" s="17">
         <f>C11-C16</f>
-        <v/>
+        <v>126856.0</v>
       </c>
       <c r="D17" s="17">
         <f>D11-D16</f>
-        <v/>
+        <v>171780.0</v>
       </c>
     </row>
     <row r="18">
@@ -1958,23 +1988,32 @@
       </c>
       <c r="B18" s="19">
         <f>B17/B11</f>
-        <v/>
+        <v>0.5704667555724899</v>
       </c>
       <c r="C18" s="19">
         <f>C17/C11</f>
-        <v/>
+        <v>0.5797806215722121</v>
       </c>
       <c r="D18" s="19">
         <f>D17/D11</f>
-        <v/>
+        <v>0.5842857142857143</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1982,7 +2021,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2005,6 +2044,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2035,7 +2075,7 @@
       </c>
       <c r="B6" s="6">
         <f>580*0.4+1450*0.6</f>
-        <v/>
+        <v>1102.0</v>
       </c>
     </row>
     <row r="7">
@@ -2046,7 +2086,7 @@
       </c>
       <c r="B7" s="7">
         <f>1-0.26-0.04-0.08</f>
-        <v/>
+        <v>0.62</v>
       </c>
     </row>
     <row r="8">
@@ -2057,7 +2097,7 @@
       </c>
       <c r="B8" s="6">
         <f>B6*B7</f>
-        <v/>
+        <v>683.24</v>
       </c>
     </row>
     <row r="9">
@@ -2068,7 +2108,7 @@
       </c>
       <c r="B9" s="20">
         <f>B5/B8</f>
-        <v/>
+        <v>11.416193431297934</v>
       </c>
     </row>
     <row r="10">
@@ -2079,15 +2119,24 @@
       </c>
       <c r="B10" s="21">
         <f>B9/12</f>
-        <v/>
+        <v>0.9513494526081612</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2095,7 +2144,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2122,6 +2171,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2436,10 +2486,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2447,7 +2506,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2472,6 +2531,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2712,9 +2772,18 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:J2"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>